--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,676 +808,700 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9159,0.0003,0.0469,0.0150</t>
-  </si>
-  <si>
-    <t>0.0102,0.0004,0.0019,0.9954</t>
-  </si>
-  <si>
-    <t>0.9803,0.0001,0.0001,0.0115</t>
-  </si>
-  <si>
-    <t>0.7068,0.0001,0.0001,0.5130</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8348,0.0013,0.0785,0.0457</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.9787,0.0001,0.0004,0.0181</t>
+  </si>
+  <si>
+    <t>0.2144,0.0000,0.0000,0.9634</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9890,0.0022,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.2287,0.0004,0.8455,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.9977,0.0005</t>
+  </si>
+  <si>
+    <t>0.9496,0.0009,0.0561,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0088,0.9916,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8881,0.0001,0.1089,0.0014</t>
+  </si>
+  <si>
+    <t>0.3022,0.0016,0.7066,0.0012</t>
+  </si>
+  <si>
+    <t>0.0102,0.0004,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0047,0.9925,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9422,0.0373,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.9933,0.0061,0.0000</t>
+  </si>
+  <si>
+    <t>0.4787,0.0005,0.4806,0.0031</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5397,0.5714,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9981,0.0066,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.2692,0.9197,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.0018,0.9895,0.0015</t>
+  </si>
+  <si>
+    <t>0.0005,0.0031,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.2296,0.0004,0.7806,0.0023</t>
+  </si>
+  <si>
+    <t>0.0025,0.0146,0.9942,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.3411,0.0001,0.9609</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0059,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0324,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0155,0.0007,0.9889,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0022,0.9950,0.0014</t>
+  </si>
+  <si>
+    <t>0.9980,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9893,0.0108,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9739,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0038,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0066,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9757,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.9979,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9991,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0012,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7093,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9876,0.9912,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.3177,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.0007,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0036,0.0004,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0006,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0006,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.7660,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.5642,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9964,0.1893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9397,0.9156,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9840,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9459,0.9761,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0038,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0112,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0002,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0612,0.0005,0.9672,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0137,0.9875,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9549,0.0021,0.0290,0.0002</t>
-  </si>
-  <si>
-    <t>0.6404,0.0042,0.3737,0.0006</t>
-  </si>
-  <si>
-    <t>0.0037,0.0003,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0008,0.9963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9684,0.0245,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9884,0.0022,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0023,0.9929,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.3329,0.0066,0.5896,0.0019</t>
-  </si>
-  <si>
-    <t>0.9133,0.0004,0.0590,0.0002</t>
-  </si>
-  <si>
-    <t>0.0400,0.9637,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0122,0.8416,0.1017,0.0008</t>
-  </si>
-  <si>
-    <t>0.0031,0.0003,0.9945,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0416,0.0005,0.9552,0.0018</t>
-  </si>
-  <si>
-    <t>0.0050,0.0024,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9982,0.0005</t>
-  </si>
-  <si>
-    <t>0.0092,0.1781,0.0000,0.7199</t>
+    <t>0.9977,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0012,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0012,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9998,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0080,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1545,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0025,0.9924,0.0043</t>
-  </si>
-  <si>
-    <t>0.9977,0.0022,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
+    <t>0.0001,0.9998,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.1223,0.8968,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.3296,0.0027,0.6859,0.0023</t>
+  </si>
+  <si>
+    <t>0.0723,0.0064,0.9129,0.0024</t>
+  </si>
+  <si>
+    <t>0.0410,0.2535,0.3963,0.0052</t>
+  </si>
+  <si>
+    <t>0.8218,0.0009,0.1743,0.0007</t>
+  </si>
+  <si>
+    <t>0.0045,0.0059,0.0122,0.9894</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.8506,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8508,0.1496,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.8519,0.1373,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9269,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.1591,0.8875,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0210,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.8597,0.0008,0.1583,0.0013</t>
+  </si>
+  <si>
+    <t>0.0072,0.0008,0.9927,0.0006</t>
+  </si>
+  <si>
+    <t>0.9874,0.0008,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.1742,0.0000,0.0000,0.9301</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0023,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9925,0.4297,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.9918,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0003,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.0940,0.9236,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7770,0.0000,0.0000,0.7458</t>
+  </si>
+  <si>
+    <t>0.0001,0.0548,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0184,0.9839,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0017,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9318,0.0566,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0037,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9904,0.0032,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.7028,0.3549,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.8129,0.2501,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9527,0.0616,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9211,0.0017,0.0816,0.0007</t>
+  </si>
+  <si>
+    <t>0.9860,0.0240,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0029,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9910,0.0079,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9474,0.0408,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9815,0.0097,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.3695,0.0254,0.3521,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0117,0.0042,0.9813,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.8608,0.0006,0.0841,0.0093</t>
+  </si>
+  <si>
+    <t>0.7967,0.0091,0.1535,0.0007</t>
+  </si>
+  <si>
+    <t>0.1058,0.1030,0.4260,0.0002</t>
+  </si>
+  <si>
+    <t>0.1507,0.0025,0.8424,0.0001</t>
+  </si>
+  <si>
+    <t>0.9567,0.0034,0.0279,0.0017</t>
+  </si>
+  <si>
+    <t>0.6643,0.0029,0.2876,0.0158</t>
+  </si>
+  <si>
+    <t>0.0125,0.9875,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9954,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.2108,0.8472,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.1956,0.8529,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.1309,0.9133,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.3766,0.3068,0.0391,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9866,0.0015,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.7224,0.0535,0.0837,0.0009</t>
+  </si>
+  <si>
+    <t>0.8876,0.0003,0.1425,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0010,0.9941,0.0023</t>
+  </si>
+  <si>
+    <t>0.0010,0.0130,0.9950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0042,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.0015,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0144,0.9885,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0032,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0017,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0014</t>
+  </si>
+  <si>
+    <t>0.0137,0.0371,0.9395,0.0021</t>
+  </si>
+  <si>
+    <t>0.2132,0.0012,0.8487,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0024,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0055,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0002,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0002,0.9912,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0053,0.9959,0.0018</t>
+  </si>
+  <si>
+    <t>0.8711,0.0003,0.1487,0.0008</t>
+  </si>
+  <si>
+    <t>0.9776,0.0002,0.0303,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0024,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9915,0.0118,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0036,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0036,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0262,0.9758,0.0021</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0001</t>
   </si>
   <si>
-    <t>0.9989,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0030,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.3224,0.8923,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9605,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9992,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9922,0.0003,0.0089,0.0001</t>
-  </si>
-  <si>
-    <t>0.8763,0.0049,0.1133,0.0018</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9392,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9888,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9904,0.6749,0.0000</t>
-  </si>
-  <si>
-    <t>0.3271,0.0003,0.0030,0.6296</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0016,0.0007,0.0019,0.9982</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0004,0.9993</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0008,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.4114,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.0196,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9621,0.9787,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9673,0.9911,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0034,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0038,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0005</t>
-  </si>
-  <si>
-    <t>0.8335,0.0007,0.0867,0.0092</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0946,0.9229,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9331,0.0040,0.0507,0.0011</t>
-  </si>
-  <si>
-    <t>0.0135,0.0011,0.9890,0.0009</t>
-  </si>
-  <si>
-    <t>0.4041,0.1544,0.0726,0.0017</t>
-  </si>
-  <si>
-    <t>0.3661,0.0011,0.6323,0.0003</t>
-  </si>
-  <si>
-    <t>0.0192,0.0016,0.0053,0.9828</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9968,0.5403,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9488,0.0523,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.8524,0.1146,0.0069,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0688,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.1194,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0083,0.0060,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0022,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9083,0.0011,0.0955,0.0021</t>
-  </si>
-  <si>
-    <t>0.0012,0.0015,0.9983,0.0006</t>
-  </si>
-  <si>
-    <t>0.9646,0.0135,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0162,0.0000,0.0002,0.9965</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9844,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9973,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6127,0.4605,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.1934,0.0000,0.0000,0.9871</t>
-  </si>
-  <si>
-    <t>0.0002,0.0020,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0000,0.0013,0.0073</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0920,0.9131,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0040,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8756,0.0946,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9887,0.0046,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9891,0.0050,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9361,0.0907,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.5750,0.4492,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.9066,0.1023,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.0075,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.9953,0.0056,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9778,0.0106,0.0027,0.0030</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9815,0.0086,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0024,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0546,0.0228,0.8482,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0038,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0643,0.0347,0.8192,0.0038</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9971,0.0024</t>
-  </si>
-  <si>
-    <t>0.4584,0.0217,0.3645,0.0005</t>
-  </si>
-  <si>
-    <t>0.2853,0.0150,0.5740,0.0004</t>
-  </si>
-  <si>
-    <t>0.0633,0.0037,0.9251,0.0002</t>
-  </si>
-  <si>
-    <t>0.9722,0.0006,0.0237,0.0008</t>
-  </si>
-  <si>
-    <t>0.9024,0.0157,0.0370,0.0026</t>
-  </si>
-  <si>
-    <t>0.0023,0.9970,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0385,0.9617,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.7174,0.4000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9304,0.0821,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.1327,0.8940,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9571,0.0167,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0005,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9828,0.0010,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.4190,0.3616,0.0198,0.0020</t>
-  </si>
-  <si>
-    <t>0.9722,0.0015,0.0197,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.0007,0.9977,0.0017</t>
-  </si>
-  <si>
-    <t>0.0082,0.0052,0.9810,0.0006</t>
-  </si>
-  <si>
-    <t>0.0066,0.0215,0.9843,0.0005</t>
-  </si>
-  <si>
-    <t>0.2876,0.0009,0.7119,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.5700,0.9188,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0022,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0203,0.9757,0.0021</t>
-  </si>
-  <si>
-    <t>0.7275,0.0003,0.2952,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0032,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0015,0.9966,0.0011</t>
-  </si>
-  <si>
-    <t>0.9917,0.0003,0.0049,0.0002</t>
-  </si>
-  <si>
-    <t>0.9727,0.0007,0.0280,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9941,0.0043,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0155,0.0051,0.9739,0.0006</t>
-  </si>
-  <si>
-    <t>0.0052,0.0002,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0888,0.9325,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.0295,0.9738,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.1192,0.0008,0.8818,0.0045</t>
-  </si>
-  <si>
-    <t>0.0109,0.0003,0.9833,0.0017</t>
-  </si>
-  <si>
-    <t>0.0552,0.0014,0.9144,0.0005</t>
-  </si>
-  <si>
-    <t>0.5656,0.0000,0.0010,0.7200</t>
-  </si>
-  <si>
-    <t>0.0031,0.0031,0.0009,0.9976</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.0024,0.9987</t>
-  </si>
-  <si>
-    <t>0.7443,0.0022,0.0007,0.2209</t>
+    <t>0.0788,0.0002,0.8990,0.0058</t>
+  </si>
+  <si>
+    <t>0.0328,0.0016,0.9630,0.0022</t>
+  </si>
+  <si>
+    <t>0.0090,0.0006,0.9856,0.0016</t>
+  </si>
+  <si>
+    <t>0.9745,0.0000,0.0015,0.0345</t>
+  </si>
+  <si>
+    <t>0.0031,0.0214,0.0012,0.9964</t>
+  </si>
+  <si>
+    <t>0.0179,0.0000,0.0004,0.9962</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.8889,0.0001,0.0006,0.1744</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1877,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1891,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1919,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1933,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1947,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1961,7 +1985,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1975,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1989,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2003,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2017,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,7 +2083,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2182,10 +2206,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2251,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2241,7 +2265,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2307,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,10 +2346,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,7 +2363,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2378,10 +2402,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2433,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2437,7 +2461,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,7 +2503,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2517,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2507,7 +2531,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2545,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2549,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2615,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2647,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2661,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2675,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2689,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2703,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2731,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2745,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2759,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2773,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2787,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2801,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2839,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2829,7 +2853,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2895,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,10 +2920,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2941,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2955,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2969,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2983,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2994,10 +3018,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3011,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3025,7 +3049,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3039,7 +3063,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,7 +3091,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3081,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3095,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3109,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3123,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3137,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3151,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3165,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3179,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3221,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3235,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3249,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3277,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3291,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>317</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3305,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>289</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3319,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3333,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3347,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3361,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3375,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3389,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3403,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3417,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3431,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,10 +3480,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,7 +3497,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,10 +3508,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3498,10 +3522,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3515,7 +3539,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3529,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3543,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3571,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3585,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3613,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3627,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>383</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3655,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3669,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3683,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3725,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,10 +3760,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,7 +3777,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3837,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3865,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3879,7 +3903,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3904,10 +3928,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3959,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3960,10 +3984,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +4001,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,10 +4012,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,7 +4085,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,7 +4127,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>356</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>411</v>
+        <v>273</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>356</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4257,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4296,10 +4320,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,10 +4460,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>289</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,10 +4544,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,7 +4561,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4548,10 +4572,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4565,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,7 +4617,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,7 +4631,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,10 +4656,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,10 +4670,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,7 +4687,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4674,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4785,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4813,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4911,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,7 +4967,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,10 +4978,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +5023,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5065,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,7 +5121,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>349</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5153,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5167,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>349</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,7 +5331,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,10 +5370,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5391,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>388</v>
+        <v>494</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5405,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5419,7 +5443,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
